--- a/business_forms/046_h_s_safety_equipment_sign_out_form--business_forms.xlsx
+++ b/business_forms/046_h_s_safety_equipment_sign_out_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'hard_hat'}</t>
+          <t>hard_hat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Hard hat'}</t>
+          <t>Hard hat</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'safety_harness'}</t>
+          <t>safety_harness</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Safety Harness'}</t>
+          <t>Safety Harness</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'safety_glasses'}</t>
+          <t>safety_glasses</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Safety Glasses'}</t>
+          <t>Safety Glasses</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'safety_harness_with_fall_arrest'}</t>
+          <t>safety_harness_with_fall_arrest</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Safety Harness with Fall Arrest'}</t>
+          <t>Safety Harness with Fall Arrest</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'hard_hat_with_earplugs'}</t>
+          <t>hard_hat_with_earplugs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Hard hat with earplugs'}</t>
+          <t>Hard hat with earplugs</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
